--- a/duty_roster/output/予定一覧_2026-10_2027-03.xlsx
+++ b/duty_roster/output/予定一覧_2026-10_2027-03.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -557,85 +557,378 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    OSCE外部評価者 (佐賀)   場所付き (終日)</t>
+          <t xml:space="preserve">    市立救急 (夜間)         夜間の予定</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>・A 列の日番号が赤い日 = 土日・祝日 (12/29〜1/3 の年末年始も赤にしています)。休日を変えるときはセルの塗りつぶしを変えてください。</t>
+          <t xml:space="preserve">    OSCE外部評価者 (佐賀)   場所付き (終日)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>・記入例として 2026-09 シートに実際の予定を入れてあります。</t>
+          <t>・A 列の日番号が赤い日 = 土日・祝日 (12/29〜1/3 の年末年始も赤にしています)。休日を変えるときはセルの塗りつぶしを変えてください。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>・記入例として 2026-09 シートに実際の予定を入れてあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>・このファイルはそのまま  python -m duty_roster parse-plan &lt;このファイル&gt; --month YYYY-MM  で読み込めます。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>祝日 (このファイルで赤にした日):</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2026-09: 9/21 敬老の日, 9/22 国民の休日, 9/23 秋分の日</t>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>定例予定 (各月に自動入力済み。変更するときはシートのセルを直接書き換えてください):</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2026-10: 10/12 スポーツの日</t>
+          <t xml:space="preserve">    全員: 毎週水曜 心臓カテーテル (AM) (除く: 偶数月第2)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2026-11: 11/3 文化の日, 11/23 勤労感謝の日</t>
+          <t xml:space="preserve">    仲本・佐々木: 第3月曜 検査 (AM)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2026-12: 12/29 年末年始, 12/30 年末年始, 12/31 年末年始</t>
+          <t xml:space="preserve">    岡﨑: 第1木曜 平鹿総合 (PM)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2027-01: 1/1 元日, 1/2 年末年始, 1/3 年末年始, 1/11 成人の日</t>
+          <t xml:space="preserve">    岡﨑: 第1金曜 日赤 (PM)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2027-02: 2/11 建国記念の日, 2/23 天皇誕生日</t>
+          <t xml:space="preserve">    岡﨑: 第2水曜 日赤 (PM)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    岡﨑: 第2金曜 日赤 (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    岡﨑: 第3木曜 平鹿総合 (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    岡﨑: 第3金曜 日赤 (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    岡﨑: 第4水曜 日赤 (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    岡﨑: 第4金曜 日赤 (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 毎週火曜 外来 (AM/PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第1金曜 由利組合 (PM) [奇数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第2金曜 由利組合 (PM) [奇数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第3金曜 大曲厚生 (PM) [奇数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第4水曜 療育センター (PM) [奇数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第1金曜 大曲厚生 (PM) [偶数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第2水曜 能代厚生 (PM) [偶数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第2金曜 由利組合 (PM) [偶数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第3金曜 大曲厚生 (PM) [偶数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第4水曜 療育センター (PM) [偶数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    仲本: 第4金曜 能代厚生 (PM) [偶数月]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    佐々木: 第1月曜 大森 (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    佐々木: 第2月曜 大森 (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    佐々木: 第3金曜 市立救急 (夜間)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    佐々木: 第4月曜 大森 (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    岡﨑: 上記以外の平日 (空いている午前/午後) は センター業務</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>土日・祝日のため入力しなかった定例予定 (必要なら手で追加してください):</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-10-12 (スポーツの日) 佐々木: 大森 (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-11-03 (文化の日) 仲本: 外来 (AM/PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-11-23 (勤労感謝の日) 佐々木: 大森 (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-12-29 (年末年始) 仲本: 外来 (AM/PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-12-30 (年末年始) 岡﨑: 心臓カテーテル (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-12-30 (年末年始) 仲本: 心臓カテーテル (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-12-30 (年末年始) 佐々木: 心臓カテーテル (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2027-01-01 (元日) 岡﨑: 日赤 (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2027-01-01 (元日) 仲本: 由利組合 (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2027-01-11 (成人の日) 佐々木: 大森 (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2027-02-23 (天皇誕生日) 仲本: 外来 (AM/PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2027-03-22 (振替休日) 佐々木: 大森 (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>祝日 (このファイルで赤にした日):</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-09: 9/21 敬老の日, 9/22 国民の休日, 9/23 秋分の日</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-10: 10/12 スポーツの日</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-11: 11/3 文化の日, 11/23 勤労感謝の日</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2026-12: 12/29 年末年始, 12/30 年末年始, 12/31 年末年始</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2027-01: 1/1 元日, 1/2 年末年始, 1/3 年末年始, 1/11 成人の日</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2027-02: 2/11 建国記念の日, 2/23 天皇誕生日</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">    2027-03: 3/21 春分の日, 3/22 振替休日</t>
         </is>
@@ -1194,7 +1487,7 @@
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>豊野</t>
+          <t>岡﨑</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -1213,7 +1506,11 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
@@ -1222,8 +1519,16 @@
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
     </row>
@@ -1249,17 +1554,33 @@
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
     </row>
@@ -1267,16 +1588,32 @@
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -1285,8 +1622,16 @@
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
@@ -1321,8 +1666,16 @@
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
     </row>
@@ -1330,8 +1683,16 @@
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>能代厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
     </row>
@@ -1339,7 +1700,11 @@
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
@@ -1348,9 +1713,21 @@
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>市立救急 (夜間)</t>
+        </is>
+      </c>
       <c r="E17" s="4" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1375,17 +1752,37 @@
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
       <c r="E20" s="4" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
     </row>
@@ -1393,16 +1790,32 @@
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E22" s="4" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
@@ -1411,8 +1824,16 @@
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>能代厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
     </row>
@@ -1438,34 +1859,66 @@
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 療育センター (PM)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="n"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
@@ -1474,7 +1927,11 @@
       <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="n"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
@@ -1514,7 +1971,7 @@
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>豊野</t>
+          <t>岡﨑</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -1542,9 +1999,17 @@
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1560,16 +2025,32 @@
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
@@ -1578,8 +2059,16 @@
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
     </row>
@@ -1605,17 +2094,33 @@
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
     </row>
@@ -1623,16 +2128,32 @@
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -1641,8 +2162,16 @@
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
     </row>
@@ -1668,17 +2197,37 @@
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
       <c r="E17" s="4" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
     </row>
@@ -1686,16 +2235,32 @@
       <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
@@ -1704,9 +2269,21 @@
       <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>市立救急 (夜間)</t>
+        </is>
+      </c>
       <c r="E21" s="4" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1740,25 +2317,49 @@
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 療育センター (PM)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
@@ -1767,7 +2368,11 @@
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
@@ -1794,7 +2399,11 @@
       <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="n"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
@@ -1825,7 +2434,7 @@
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>豊野</t>
+          <t>岡﨑</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -1844,8 +2453,16 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
     </row>
@@ -1853,16 +2470,32 @@
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
@@ -1871,8 +2504,16 @@
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
     </row>
@@ -1898,17 +2539,33 @@
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
     </row>
@@ -1916,8 +2573,16 @@
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>能代厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
@@ -1925,7 +2590,11 @@
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -1934,8 +2603,16 @@
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
     </row>
@@ -1961,17 +2638,33 @@
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
     </row>
@@ -1979,16 +2672,32 @@
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E17" s="4" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
@@ -1997,9 +2706,21 @@
       <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>市立救急 (夜間)</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2024,34 +2745,70 @@
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
       <c r="E22" s="4" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 療育センター (PM)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E24" s="4" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
@@ -2060,8 +2817,16 @@
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>能代厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
     </row>
@@ -2087,9 +2852,17 @@
       <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2145,7 +2918,7 @@
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>豊野</t>
+          <t>岡﨑</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -2191,17 +2964,33 @@
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
     </row>
@@ -2209,16 +2998,32 @@
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
@@ -2227,8 +3032,16 @@
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
     </row>
@@ -2263,8 +3076,16 @@
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
     </row>
@@ -2272,16 +3093,32 @@
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
@@ -2290,9 +3127,21 @@
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>市立救急 (夜間)</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2317,17 +3166,37 @@
       <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
     </row>
@@ -2335,16 +3204,32 @@
       <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E21" s="4" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
@@ -2353,7 +3238,11 @@
       <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
@@ -2380,34 +3269,66 @@
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 療育センター (PM)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E28" s="4" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
@@ -2416,7 +3337,11 @@
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="n"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
@@ -2465,7 +3390,7 @@
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>豊野</t>
+          <t>岡﨑</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -2484,17 +3409,33 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E2" s="4" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
     </row>
@@ -2502,16 +3443,32 @@
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
@@ -2520,8 +3477,16 @@
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
     </row>
@@ -2547,17 +3512,33 @@
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
@@ -2565,8 +3546,16 @@
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>能代厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
     </row>
@@ -2583,8 +3572,16 @@
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
     </row>
@@ -2610,17 +3607,37 @@
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
     </row>
@@ -2628,16 +3645,32 @@
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E18" s="4" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
@@ -2646,9 +3679,21 @@
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>市立救急 (夜間)</t>
+        </is>
+      </c>
       <c r="E20" s="4" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2673,9 +3718,17 @@
       <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E23" s="4" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2687,20 +3740,36 @@
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 療育センター (PM)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
@@ -2709,8 +3778,16 @@
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>能代厚生 (PM)</t>
+        </is>
+      </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
     </row>
@@ -2758,7 +3835,7 @@
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>豊野</t>
+          <t>岡﨑</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -2777,17 +3854,33 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E2" s="4" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
     </row>
@@ -2795,16 +3888,32 @@
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
@@ -2813,8 +3922,16 @@
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
     </row>
@@ -2840,17 +3957,33 @@
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>大森 (AM)</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
@@ -2858,16 +3991,32 @@
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
@@ -2876,8 +4025,16 @@
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>由利組合 (PM)</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
     </row>
@@ -2903,17 +4060,37 @@
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>検査 (AM)</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
     </row>
@@ -2921,16 +4098,32 @@
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E18" s="4" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 平鹿総合 (PM)</t>
+        </is>
+      </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
@@ -2939,9 +4132,21 @@
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>大曲厚生 (PM)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>市立救急 (夜間)</t>
+        </is>
+      </c>
       <c r="E20" s="4" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2975,25 +4180,49 @@
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 日赤 (PM)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), 療育センター (PM)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
@@ -3002,7 +4231,11 @@
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>センター業務 (AM), 日赤 (PM)</t>
+        </is>
+      </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
@@ -3029,7 +4262,11 @@
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="n"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
@@ -3038,8 +4275,16 @@
       <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>センター業務</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>外来 (AM/PM)</t>
+        </is>
+      </c>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
     </row>
@@ -3047,9 +4292,21 @@
       <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM), センター業務 (PM)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>心臓カテーテル (AM)</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="n"/>
     </row>
   </sheetData>
